--- a/test/excel/win/parts/struct-held/copy-fill.xlsx
+++ b/test/excel/win/parts/struct-held/copy-fill.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xlcalc\work\parts-struct-held-45796-1\out\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xlcalc\work\parts-struct-held-30311-1\out\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6774657-3B03-4390-93C5-96E1BD1ED95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D22CEA7-02B9-4903-9349-1C39DB9D5966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
     <author>Ann</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{91B6CC24-3D0E-47BD-83F0-7F69D0E2072F}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{A9385D9F-BCAB-4FA0-B160-11374EDFB35E}">
       <text>
         <r>
           <rPr>
@@ -48,7 +48,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{3B6487E8-384D-45BF-AC51-776306250FF9}">
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{1C0B852C-33C8-4E4A-8ECE-D92CC5144AFB}">
       <text>
         <r>
           <rPr>
@@ -70,7 +70,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{27CA7B81-95A4-4BCD-A489-06F8AFD6133C}">
+    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{C5D0650B-22FB-4540-9DC1-CFFFCE60B172}">
       <text>
         <r>
           <rPr>
@@ -577,9 +577,9 @@
     <hyperlink ref="B3" r:id="rId1" tooltip="B3" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="C5" location="S!A1" display="to A1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="D6" location="'T'!A1" display="to T" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="F2" r:id="rId2" tooltip="B3" xr:uid="{5B42CF52-5F34-46FD-AF70-C3146FE6A1CD}"/>
-    <hyperlink ref="F4" r:id="rId3" tooltip="B3" xr:uid="{5FE4180A-1EE9-43D5-AF2E-0377AEFBB7FF}"/>
-    <hyperlink ref="F6" r:id="rId4" tooltip="B3" xr:uid="{85DEE492-B27C-4A13-9822-67DFC3B3BE5B}"/>
+    <hyperlink ref="F2" r:id="rId2" tooltip="B3" xr:uid="{BF8F9B8D-39B0-49ED-A355-CB746D093B55}"/>
+    <hyperlink ref="F4" r:id="rId3" tooltip="B3" xr:uid="{DF230104-6BD1-417B-AABD-44D44FE0A2DD}"/>
+    <hyperlink ref="F6" r:id="rId4" tooltip="B3" xr:uid="{82C8B116-705B-4CC6-AB05-05117B96CDD9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId5"/>
